--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484064_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484064_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5192</v>
+        <v>7.6762</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4752</v>
+        <v>6.0116</v>
       </c>
       <c r="F2" t="n">
-        <v>2.044</v>
+        <v>1.6646</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5303</v>
+        <v>6.8734</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3356</v>
+        <v>1.1796</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1947</v>
+        <v>5.6939</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7519</v>
+        <v>6.8935</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5832</v>
+        <v>1.2256</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1687</v>
+        <v>5.6679</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2216</v>
+        <v>-0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2477</v>
+        <v>-0.046</v>
       </c>
       <c r="O2" t="n">
         <v>0.026</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3806</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-4.9596</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3806</v>
+        <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8148</v>
+        <v>0.3061</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7233</v>
+        <v>-0.0736</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0915</v>
+        <v>0.3797</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2065</v>
+        <v>2.6789</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4.1513</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.021</v>
+        <v>6.0166</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5809</v>
+        <v>4.4776</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4401</v>
+        <v>1.539</v>
       </c>
       <c r="G3" t="n">
-        <v>6.8734</v>
+        <v>3.5303</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1796</v>
+        <v>1.3356</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6939</v>
+        <v>2.1947</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8935</v>
+        <v>3.7519</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2256</v>
+        <v>1.5832</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6679</v>
+        <v>2.1687</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02</v>
+        <v>-0.2216</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.046</v>
+        <v>-0.2477</v>
       </c>
       <c r="O3" t="n">
         <v>0.026</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.9596</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7774</v>
+        <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3491</v>
+        <v>1.3122</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5044</v>
+        <v>0.7256</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1552</v>
+        <v>0.5865</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6789</v>
+        <v>-1.2065</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1513</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8467</v>
+        <v>4.6997</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6149</v>
+        <v>3.1874</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2318</v>
+        <v>1.5123</v>
       </c>
       <c r="G4" t="n">
         <v>3.9681</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7085</v>
+        <v>0.1446</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3173</v>
+        <v>0.2552</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3912</v>
+        <v>-0.1106</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6032</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8754</v>
+        <v>2.8536</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1833</v>
+        <v>1.2456</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6921</v>
+        <v>1.608</v>
       </c>
       <c r="G5" t="n">
         <v>1.6789</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6014</v>
+        <v>0.5796</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3175</v>
+        <v>0.3798</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2839</v>
+        <v>0.1997</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3065</v>
+        <v>2.0104</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3068</v>
+        <v>1.4315</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9997</v>
+        <v>0.5789</v>
       </c>
       <c r="G6" t="n">
         <v>1.3231</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>0.666</v>
+        <v>0.3698</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1928</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5979</v>
+        <v>0.1771</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6745</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8289</v>
+        <v>1.8669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1741</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6548</v>
+        <v>1.9451</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6109</v>
+        <v>2.2783</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9296</v>
+        <v>0.5694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3187</v>
+        <v>1.7088</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.922</v>
+        <v>2.5834</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0852</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1632</v>
+        <v>1.9679</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3111</v>
+        <v>-0.3051</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1556</v>
+        <v>-0.046</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1555</v>
+        <v>-0.2591</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5786</v>
+        <v>0.136</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6155</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0369</v>
+        <v>0.0679</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8692</v>
+        <v>-0.7458</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4724</v>
+        <v>-0.7458</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.926</v>
+        <v>1.3173</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0191</v>
+        <v>-0.4778</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9451</v>
+        <v>1.7951</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2783</v>
+        <v>-1.6109</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5694</v>
+        <v>-1.9296</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7088</v>
+        <v>0.3187</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5834</v>
+        <v>-1.922</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6153999999999999</v>
+        <v>-2.0852</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9679</v>
+        <v>0.1632</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3051</v>
+        <v>0.3111</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.046</v>
+        <v>0.1556</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2591</v>
+        <v>0.1555</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8048999999999999</v>
+        <v>1.067</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8728</v>
+        <v>0.9637</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0679</v>
+        <v>0.1034</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7458</v>
+        <v>0.8692</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7458</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6106</v>
+        <v>0.3949</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8736</v>
+        <v>1.6299</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.263</v>
+        <v>-1.235</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3604</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3758</v>
+        <v>0.1601</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7652</v>
+        <v>0.5215</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3894</v>
+        <v>-0.3614</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.609</v>
+        <v>-0.3387</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8521</v>
+        <v>-0.7501</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2431</v>
+        <v>0.4114</v>
       </c>
       <c r="G10" t="n">
         <v>0.3411</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3469</v>
+        <v>-0.0765</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0975</v>
+        <v>0.0708</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1632</v>
+        <v>-1.0666</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5519</v>
+        <v>-1.4272</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3887</v>
+        <v>0.3606</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7911</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1797</v>
+        <v>0.2763</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3288</v>
+        <v>0.4535</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1491</v>
+        <v>-0.1772</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5437</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3739</v>
+        <v>-1.0693</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8303</v>
+        <v>-2.666</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4564</v>
+        <v>1.5967</v>
       </c>
       <c r="G12" t="n">
         <v>0.5051</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1049</v>
+        <v>0.4095</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2041</v>
+        <v>0.3685</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0993</v>
+        <v>0.041</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4143</v>
+        <v>-3.0521</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.306</v>
+        <v>-0.9999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1083</v>
+        <v>-2.0522</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3189</v>
@@ -1468,13 +1468,13 @@
         <v>0.1984</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0873</v>
+        <v>0.2749</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0113</v>
+        <v>0.3174</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0425</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.3739</v>
+        <v>21.3089</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6494</v>
+        <v>11.5844</v>
       </c>
       <c r="F14" t="n">
-        <v>9.724500000000001</v>
+        <v>9.724499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>15.417</v>
@@ -1546,16 +1546,16 @@
         <v>20.8302</v>
       </c>
       <c r="S14" t="n">
-        <v>4.024500000000001</v>
+        <v>4.959599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0899</v>
+        <v>4.025099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9343999999999999</v>
+        <v>0.9344</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.035299999999999</v>
+        <v>-3.0353</v>
       </c>
       <c r="W14" t="n">
         <v>5.3386</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5825</v>
+        <v>1.0917</v>
       </c>
       <c r="E15" t="n">
-        <v>1.839</v>
+        <v>1.5282</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2565</v>
+        <v>-0.4365</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5812</v>
+        <v>-0.5903</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3712</v>
+        <v>-0.0501</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9524</v>
+        <v>-0.5402</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5304</v>
+        <v>1.5885</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4877</v>
+        <v>0.9433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0427</v>
+        <v>0.6451</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1116</v>
+        <v>-2.1788</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1165</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9951</v>
+        <v>-1.1853</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>1.612</v>
+        <v>-0.0482</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6892</v>
+        <v>0.0624</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0772</v>
+        <v>-0.1106</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3452</v>
+        <v>0.9367</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6032</v>
+        <v>0.8692</v>
       </c>
       <c r="X15" t="n">
-        <v>0.742</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7341</v>
+        <v>0.3956</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4254</v>
+        <v>0.7167</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1594</v>
+        <v>-0.3211</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4755</v>
+        <v>-0.5812</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.232</v>
+        <v>1.3712</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2435</v>
+        <v>-1.9524</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7082000000000001</v>
+        <v>1.5304</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0255</v>
+        <v>1.4877</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6827</v>
+        <v>0.0427</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1837</v>
+        <v>-2.1116</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2574</v>
+        <v>-0.1165</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9263</v>
+        <v>-1.9951</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>0.535</v>
+        <v>0.4251</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0567</v>
+        <v>0.5669</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4783</v>
+        <v>-0.1418</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6745</v>
+        <v>1.3452</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6745</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1513</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.916</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7647</v>
+        <v>0.8228</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5903</v>
+        <v>-0.4755</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0501</v>
+        <v>-0.232</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5402</v>
+        <v>-0.2435</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5885</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9433</v>
+        <v>0.0255</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6451</v>
+        <v>0.6827</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1788</v>
+        <v>-1.1837</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.2574</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1853</v>
+        <v>-0.9263</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9886</v>
+        <v>-0.1077</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5498</v>
+        <v>-0.2493</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4388</v>
+        <v>0.1416</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9367</v>
+        <v>0.6745</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0675</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0196</v>
+        <v>-0.7331</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3735</v>
+        <v>-1.4755</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3539</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5644</v>
@@ -1858,13 +1858,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4551</v>
+        <v>-0.1686</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1304</v>
+        <v>0.0284</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5856</v>
+        <v>-0.197</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8819</v>
+        <v>-1.9321</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.362</v>
+        <v>-0.464</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.52</v>
+        <v>-1.4681</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5352</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0051</v>
+        <v>-0.0553</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1814</v>
+        <v>0.0794</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1865</v>
+        <v>-0.1347</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7384</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0152</v>
+        <v>-2.5854</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3733</v>
+        <v>-2.9059</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3885</v>
+        <v>0.3206</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3099</v>
+        <v>-0.4985</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3224</v>
+        <v>0.3474</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9875</v>
+        <v>-0.8459</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5279</v>
+        <v>0.4836</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0796</v>
+        <v>0.4032</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6075</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8378</v>
+        <v>-0.9821</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2428</v>
+        <v>-0.0558</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.595</v>
+        <v>-0.9263</v>
       </c>
       <c r="P20" t="n">
         <v>-1.3887</v>
@@ -2014,28 +2014,28 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6755</v>
+        <v>-0.4322</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0034</v>
+        <v>-0.2153</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6721</v>
+        <v>-0.2168</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0079</v>
+        <v>-0.266</v>
       </c>
       <c r="W20" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0082</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1899</v>
+        <v>-3.1663</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.314</v>
+        <v>0.4551</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1242</v>
+        <v>-3.6214</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4985</v>
+        <v>-3.3099</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3474</v>
+        <v>-0.3224</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8459</v>
+        <v>-2.9875</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4836</v>
+        <v>0.5279</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4032</v>
+        <v>-0.0796</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0803</v>
+        <v>0.6075</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9821</v>
+        <v>-3.8378</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0558</v>
+        <v>-0.2428</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9263</v>
+        <v>-3.595</v>
       </c>
       <c r="P21" t="n">
         <v>-1.3887</v>
@@ -2092,22 +2092,22 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0367</v>
+        <v>0.5243</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0852</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4132</v>
+        <v>0.4391</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.266</v>
+        <v>1.0079</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.0162</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.266</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.328</v>
+        <v>-3.5875</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7493</v>
+        <v>-1.3412</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5788</v>
+        <v>-2.2463</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3389</v>
@@ -2170,13 +2170,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5922</v>
+        <v>-0.8516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7991</v>
+        <v>-0.391</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.793</v>
+        <v>-0.4606</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1985</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6989</v>
+        <v>-3.6481</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2159</v>
+        <v>-3.5017</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.483</v>
+        <v>-0.1464</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5226</v>
@@ -2248,13 +2248,13 @@
         <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1845</v>
+        <v>-1.1336</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3489</v>
+        <v>-0.6347</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8356</v>
+        <v>-0.4989</v>
       </c>
       <c r="V23" t="n">
         <v>2.4129</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7082</v>
+        <v>-4.9396</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4129</v>
+        <v>-2.0047</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2953</v>
+        <v>-2.9348</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0005</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5848</v>
+        <v>-0.8162</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6744</v>
+        <v>-0.2663</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9104</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.139</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.3738</v>
+        <v>-19.0135</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.7247</v>
+        <v>-9.724399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.6493</v>
+        <v>-9.2888</v>
       </c>
       <c r="G25" t="n">
         <v>-15.417</v>
@@ -2404,13 +2404,13 @@
         <v>16.8628</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.0245</v>
+        <v>-2.664</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9346</v>
+        <v>-0.9343</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0899</v>
+        <v>-1.7296</v>
       </c>
       <c r="V25" t="n">
         <v>3.0353</v>
